--- a/data/trans_camb/P1419-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1419-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-2,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,31</t>
+          <t>-9,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,03</t>
+          <t>-5,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,69</t>
+          <t>-5,81; -0,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,11</t>
+          <t>-5,97; -0,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -0,8</t>
+          <t>-5,74; -0,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,77; -0,89</t>
+          <t>-11,1; -0,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 0,67</t>
+          <t>-9,14; 0,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -5,41</t>
+          <t>-14,06; -5,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -1,76</t>
+          <t>-7,02; -1,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; -0,42</t>
+          <t>-6,14; -0,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -3,91</t>
+          <t>-8,6; -3,78</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-77,62%</t>
+          <t>-75,31%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-84,36%</t>
+          <t>-83,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-82,69%</t>
+          <t>-81,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,66</t>
+          <t>-100,0; -2,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-93,8; 43,57</t>
+          <t>-93,32; 35,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-95,22; -17,6</t>
+          <t>-95,12; -21,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,29; -9,38</t>
+          <t>-76,64; 2,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,89; 9,92</t>
+          <t>-64,11; 14,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,58; -66,78</t>
+          <t>-92,21; -64,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-80,03; -29,36</t>
+          <t>-77,69; -26,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,65; -4,09</t>
+          <t>-67,43; -2,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,0; -65,98</t>
+          <t>-90,38; -64,43</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,13</t>
+          <t>-4,55; -0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; -1,93</t>
+          <t>-5,86; -1,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,18</t>
+          <t>-3,59; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; -1,1</t>
+          <t>-8,45; -1,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; -5,6</t>
+          <t>-11,73; -5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,12</t>
+          <t>-3,92; 2,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -1,64</t>
+          <t>-5,72; -1,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; -4,22</t>
+          <t>-7,99; -4,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,32</t>
+          <t>-2,87; 1,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,0%</t>
+          <t>-24,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,36%</t>
+          <t>-4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,79%</t>
+          <t>-9,25%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-87,45; 6,9</t>
+          <t>-87,67; 5,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -65,87</t>
+          <t>-100,0; -60,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 55,56</t>
+          <t>-68,38; 55,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,51; -12,84</t>
+          <t>-65,71; -13,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,43; -58,12</t>
+          <t>-90,67; -58,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 37,72</t>
+          <t>-31,47; 31,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,65; -25,24</t>
+          <t>-66,42; -24,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,58; -67,48</t>
+          <t>-91,93; -67,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 20,73</t>
+          <t>-33,72; 26,56</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,92</t>
+          <t>-1,29; 1,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,17</t>
+          <t>-1,18; 2,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,2</t>
+          <t>0,95; 5,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,57</t>
+          <t>-5,29; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,08</t>
+          <t>1,71; 10,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,17</t>
+          <t>-1,02; 5,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,2</t>
+          <t>-2,52; 1,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,88</t>
+          <t>0,98; 6,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,64</t>
+          <t>0,58; 4,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302,48%</t>
+          <t>299,36%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1400,38</t>
+          <t>30,58; 1693,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,65; 44,36</t>
+          <t>-66,84; 38,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,18; 267,51</t>
+          <t>18,98; 241,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 128,17</t>
+          <t>-13,32; 134,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 48,72</t>
+          <t>-55,58; 54,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,67; 233,85</t>
+          <t>17,94; 238,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,72; 187,02</t>
+          <t>10,54; 197,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,83</t>
+          <t>-5,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-2,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,43</t>
+          <t>-2,47; 1,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,97</t>
+          <t>-2,12; 2,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,74</t>
+          <t>-1,47; 3,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,89</t>
+          <t>-5,11; 4,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 0,15</t>
+          <t>-8,85; 0,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,16; -3,09</t>
+          <t>-9,35; -1,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,1</t>
+          <t>-2,99; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,0</t>
+          <t>-4,65; 0,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -1,04</t>
+          <t>-4,95; -0,32</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-56,11%</t>
+          <t>-45,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-42,53%</t>
+          <t>-35,11%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-92,28; 247,75</t>
+          <t>-100,0; 217,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,27; 265,38</t>
+          <t>-77,4; 232,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 351,23</t>
+          <t>-67,52; 344,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 50,62</t>
+          <t>-36,32; 47,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,52; 2,92</t>
+          <t>-61,34; 5,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,28; -32,06</t>
+          <t>-62,03; -18,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 35,97</t>
+          <t>-35,9; 47,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,16; 0,44</t>
+          <t>-56,98; 9,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,85; -16,61</t>
+          <t>-56,22; -2,31</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,33</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,68</t>
+          <t>8,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,04</t>
+          <t>-1,63; 4,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,86</t>
+          <t>-2,18; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,25</t>
+          <t>1,91; 7,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 15,62</t>
+          <t>3,22; 15,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -0,35</t>
+          <t>-8,97; 0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,79; 18,59</t>
+          <t>6,59; 16,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,06</t>
+          <t>1,99; 9,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,55</t>
+          <t>-4,66; 0,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 12,69</t>
+          <t>5,68; 11,84</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>340,76%</t>
+          <t>327,37%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>181,7%</t>
+          <t>165,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>218,3%</t>
+          <t>197,39%</t>
         </is>
       </c>
     </row>
@@ -1652,42 +1652,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-98,7; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16,0; 1856,45</t>
+          <t>23,47; 1577,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,39; 318,02</t>
+          <t>32,19; 345,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-85,37; 1,23</t>
+          <t>-86,71; 10,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,05; 430,22</t>
+          <t>54,91; 373,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,48; 295,15</t>
+          <t>34,63; 297,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,67; 19,48</t>
+          <t>-72,58; 32,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>95,54; 476,06</t>
+          <t>91,57; 441,95</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,12</t>
+          <t>-3,08; 1,15</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,26</t>
+          <t>-3,16; 1,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,51</t>
+          <t>-0,45; 4,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,34</t>
+          <t>-9,36; 1,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,54; -1,9</t>
+          <t>-11,34; -1,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,77</t>
+          <t>-2,59; 7,3</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,57</t>
+          <t>-5,22; 0,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,48; -1,03</t>
+          <t>-6,2; -0,83</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,98</t>
+          <t>-0,81; 4,95</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118,85%</t>
+          <t>123,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 348,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 362,67</t>
+          <t>-100,0; 258,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 737,98</t>
+          <t>-25,49; 876,52</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-61,55; 13,51</t>
+          <t>-61,2; 16,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,08; -16,5</t>
+          <t>-77,76; -12,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 87,94</t>
+          <t>-16,22; 86,01</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 11,29</t>
+          <t>-60,3; 13,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-76,04; -15,84</t>
+          <t>-72,83; -9,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 91,02</t>
+          <t>-9,55; 94,13</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,84</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>13,51</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>10,35</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,66</t>
+          <t>-2,08; 0,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,24</t>
+          <t>-1,03; 2,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,27</t>
+          <t>4,51; 9,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,21</t>
+          <t>-1,31; 5,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,29</t>
+          <t>-5,5; 0,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 15,27</t>
+          <t>10,27; 16,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,52</t>
+          <t>-0,95; 2,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,52</t>
+          <t>-2,61; 0,63</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,17</t>
+          <t>8,24; 12,52</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>442,55%</t>
+          <t>440,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>103,73%</t>
+          <t>164,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>167,3%</t>
+          <t>209,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 97,72</t>
+          <t>-85,04; 101,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 255,47</t>
+          <t>-51,39; 232,54</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>162,34; 1124,62</t>
+          <t>174,78; 1080,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 78,53</t>
+          <t>-13,66; 77,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 6,47</t>
+          <t>-55,06; 3,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 202,93</t>
+          <t>98,61; 258,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 60,28</t>
+          <t>-16,08; 62,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 14,69</t>
+          <t>-44,43; 16,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>55,77; 255,8</t>
+          <t>141,62; 316,32</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,65</t>
+          <t>-4,3</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-10,2</t>
+          <t>-10,26</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-7,77</t>
+          <t>-7,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -3,09</t>
+          <t>-6,54; -2,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -1,99</t>
+          <t>-5,82; -2,02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -2,78</t>
+          <t>-6,15; -2,53</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -4,11</t>
+          <t>-10,13; -3,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -4,95</t>
+          <t>-11,08; -4,89</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,07; -7,26</t>
+          <t>-13,49; -7,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,08; -4,1</t>
+          <t>-7,89; -4,13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -4,11</t>
+          <t>-7,82; -4,02</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,74; -6,03</t>
+          <t>-9,19; -5,65</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-80,06%</t>
+          <t>-74,0%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-68,78%</t>
+          <t>-69,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-74,42%</t>
+          <t>-70,55%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-92,52; -64,82</t>
+          <t>-91,6; -62,88</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-82,43; -40,91</t>
+          <t>-82,29; -40,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-92,93; -59,29</t>
+          <t>-86,71; -51,34</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-62,54; -30,25</t>
+          <t>-61,74; -29,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-66,67; -36,96</t>
+          <t>-66,47; -36,07</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-77,39; -56,3</t>
+          <t>-77,96; -58,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-68,68; -44,58</t>
+          <t>-68,27; -44,93</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-68,54; -43,26</t>
+          <t>-67,81; -43,27</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-83,95; -65,3</t>
+          <t>-78,19; -60,22</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -1,15</t>
+          <t>-2,59; -1,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,26; -0,78</t>
+          <t>-2,23; -0,76</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,4</t>
+          <t>-0,08; 1,64</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,93</t>
+          <t>-3,76; -1,06</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -3,19</t>
+          <t>-6,07; -3,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,67</t>
+          <t>-1,22; 1,54</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -1,25</t>
+          <t>-2,84; -1,27</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -2,34</t>
+          <t>-3,86; -2,26</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,86</t>
+          <t>-0,36; 1,4</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-7,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-73,17; -40,89</t>
+          <t>-73,59; -41,53</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -30,11</t>
+          <t>-64,25; -28,07</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 53,62</t>
+          <t>-2,19; 63,24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-32,04; -9,15</t>
+          <t>-32,33; -10,1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-52,16; -31,78</t>
+          <t>-52,62; -32,44</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 6,52</t>
+          <t>-10,55; 15,49</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-40,05; -18,9</t>
+          <t>-39,02; -19,61</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-51,73; -34,87</t>
+          <t>-51,78; -34,24</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 13,3</t>
+          <t>-4,72; 22,54</t>
         </is>
       </c>
     </row>
